--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/biobio.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/biobio.xlsx
@@ -562,7 +562,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1789,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2565,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2630,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2695,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2760,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2825,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2890,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2955,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3020,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3207,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3272,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3398,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3463,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3589,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3715,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3780,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3845,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3971,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4036,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4223,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4288,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4353,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4418,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4544,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4731,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4796,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4922,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5170,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5235,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5300,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5365,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5430,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5495,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5621,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5808,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5873,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5938,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6003,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6068,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6133,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6320,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6385,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6450,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6576,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6641,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6706,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6771,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6836,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6901,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7027,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7153,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7279,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7344,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7409,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7474,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7539,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7604,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7669,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7734,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7799,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7864,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7929,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8055,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8120,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8246,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8311,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8376,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8441,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8506,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8632,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8697,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8762,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8827,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8892,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8957,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9083,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9453,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9518,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9583,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9648,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9713,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9778,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9843,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9908,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9973,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10038,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10103,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10168,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10233,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10298,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10363,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10428,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10554,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10619,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10745,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10871,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10997,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11123,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11249,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11314,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11379,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11444,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11509,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11635,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11700,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11765,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11830,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11895,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11960,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12086,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12212,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12277,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12342,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12468,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12533,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12659,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12724,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12850,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12915,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12980,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13106,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13171,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13236,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13301,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13427,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13553,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13679,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13744,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13809,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13874,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13939,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14004,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14069,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14134,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14199,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14264,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14329,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14394,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14520,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14585,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14650,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14715,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14902,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14967,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15032,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15097,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15223,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15288,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15353,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15418,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15483,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15548,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15613,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15739,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15804,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16113,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16239,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16304,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16552,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16617,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16682,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16747,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16873,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16938,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17003,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17068,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17133,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17198,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17324,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17389,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17515,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17702,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17828,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17893,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17958,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18023,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18088,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18214,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18279,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18344,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18409,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18474,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18539,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18604,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18669,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18856,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18982,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19108,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19173,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19238,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19303,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19429,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19494,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19559,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19624,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19689,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19876,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19941,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20006,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20071,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20197,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20262,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20327,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20392,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20457,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20522,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20587,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20652,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20717,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20782,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20847,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20912,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20977,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21042,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21107,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21172,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21237,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21302,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21367,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21432,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21558,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21688,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21753,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21818,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21944,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +22009,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22074,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22139,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22204,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22269,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22395,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22460,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22586,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/biobio.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M346"/>
+  <dimension ref="A1:M355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1871,7 +1871,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4020-248-CM25</t>
+          <t>4020-247-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1911,32 +1911,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2817.92</v>
+        <v>2449.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4020-247-CM25</t>
+          <t>4020-248-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1976,22 +1972,26 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2449.02</v>
+        <v>2817.92</v>
       </c>
     </row>
     <row r="25">
@@ -2517,7 +2517,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4074-112-CM25</t>
+          <t>4074-110-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>18653.25</v>
+        <v>11138.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4074-110-CM25</t>
+          <t>4074-111-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11138.4</v>
+        <v>9158.84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4074-111-CM25</t>
+          <t>4074-112-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9158.84</v>
+        <v>18653.25</v>
       </c>
     </row>
     <row r="36">
@@ -2842,7 +2842,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4081-82-CM25</t>
+          <t>4358-62-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2632.28</v>
+        <v>28399.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4358-62-CM25</t>
+          <t>4081-82-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>28399.35</v>
+        <v>2632.28</v>
       </c>
     </row>
     <row r="40">
@@ -4435,7 +4435,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4083-224-CM25</t>
+          <t>2409-422-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4475,28 +4475,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7257.66</v>
+        <v>12148.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2409-422-CM25</t>
+          <t>4083-224-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4521,12 +4525,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4536,26 +4540,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12148.86</v>
+        <v>7257.66</v>
       </c>
     </row>
     <row r="65">
@@ -4622,7 +4622,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2418-38-CM25</t>
+          <t>2418-37-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4662,28 +4662,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>16276.58</v>
+        <v>8419.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2418-37-CM25</t>
+          <t>2418-38-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4723,26 +4727,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8419.25</v>
+        <v>16276.58</v>
       </c>
     </row>
     <row r="68">
@@ -4874,7 +4874,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4020-537-CM25</t>
+          <t>831-116-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4914,32 +4914,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7164.87</v>
+        <v>15648.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>831-116-CM25</t>
+          <t>4020-537-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4964,12 +4960,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4979,22 +4975,26 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>15648.74</v>
+        <v>7164.87</v>
       </c>
     </row>
     <row r="72">
@@ -5955,7 +5955,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>980313-158-CM25</t>
+          <t>4081-178-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.250.900-5</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTUCO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>33051.06</v>
+        <v>3416.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4081-178-CM25</t>
+          <t>2409-640-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6079,13 +6079,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3416.25</v>
+        <v>23230.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>980313-157-CM25</t>
+          <t>2409-641-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.250.900-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTUCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6125,32 +6125,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5222.48</v>
+        <v>26731.73</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>980313-156-CM25</t>
+          <t>2409-642-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6175,12 +6171,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.250.900-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTUCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6190,28 +6186,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3562.86</v>
+        <v>16610.58</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2409-641-CM25</t>
+          <t>980313-156-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.250.900-5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6266,13 +6266,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>26731.73</v>
+        <v>3562.86</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2409-642-CM25</t>
+          <t>980313-157-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.250.900-5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6331,13 +6331,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>16610.58</v>
+        <v>5222.48</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2409-640-CM25</t>
+          <t>980313-158-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.250.900-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>23230.51</v>
+        <v>33051.06</v>
       </c>
     </row>
     <row r="94">
@@ -6467,7 +6467,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2409-617-CM25</t>
+          <t>4020-685-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6507,22 +6507,26 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2832.2</v>
+        <v>3072.46</v>
       </c>
     </row>
     <row r="96">
@@ -6593,7 +6597,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4020-685-CM25</t>
+          <t>2409-617-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6618,12 +6622,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6633,26 +6637,22 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3072.46</v>
+        <v>2832.2</v>
       </c>
     </row>
     <row r="98">
@@ -6723,7 +6723,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1389183-252-CM25</t>
+          <t>2418-50-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6748,12 +6748,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6763,26 +6763,22 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>43362.27</v>
+        <v>9377.200000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6918,7 +6914,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2418-50-CM25</t>
+          <t>1389183-252-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6943,12 +6939,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6958,22 +6954,26 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9377.200000000001</v>
+        <v>43362.27</v>
       </c>
     </row>
     <row r="103">
@@ -7751,7 +7751,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3305-433-CM25</t>
+          <t>4083-406-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.141.801-4</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7791,32 +7791,28 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4417.09</v>
+        <v>10627.89</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1057931-37-CM25</t>
+          <t>2409-929-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7836,17 +7832,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7856,17 +7852,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7875,13 +7871,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8829.799999999999</v>
+        <v>18641.23</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4079-460-CM25</t>
+          <t>1057931-37-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7906,12 +7902,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7921,17 +7917,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7940,13 +7936,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3885.74</v>
+        <v>8829.799999999999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4083-406-CM25</t>
+          <t>3305-433-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7971,12 +7967,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.141.801-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7986,28 +7982,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>10627.89</v>
+        <v>4417.09</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2409-929-CM25</t>
+          <t>4079-460-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8027,17 +8027,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>18641.23</v>
+        <v>3885.74</v>
       </c>
     </row>
     <row r="120">
@@ -8263,7 +8263,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4239-478-CM25</t>
+          <t>2418-59-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.160.201-K</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8322,13 +8322,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5401.17</v>
+        <v>2905.98</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2418-59-CM25</t>
+          <t>4239-478-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8348,17 +8348,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.201-K</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2905.98</v>
+        <v>5401.17</v>
       </c>
     </row>
     <row r="125">
@@ -8523,7 +8523,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3892-746-CM25</t>
+          <t>1389183-382-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8563,28 +8563,32 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>16362.5</v>
+        <v>10490.59</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1389183-382-CM25</t>
+          <t>3892-746-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8609,12 +8613,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8624,26 +8628,22 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>10490.59</v>
+        <v>16362.5</v>
       </c>
     </row>
     <row r="129">
@@ -9600,7 +9600,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1084156-3249-CM25</t>
+          <t>1057931-85-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9659,13 +9659,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3012.75</v>
+        <v>38769.13</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1057931-85-CM25</t>
+          <t>1084156-3249-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>38769.13</v>
+        <v>3012.75</v>
       </c>
     </row>
     <row r="146">
@@ -11014,7 +11014,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2418-78-CM25</t>
+          <t>2418-84-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11054,28 +11054,32 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6930.5</v>
+        <v>10254.23</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2418-84-CM25</t>
+          <t>2418-85-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11115,32 +11119,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10254.23</v>
+        <v>5910.05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2418-85-CM25</t>
+          <t>4020-1267-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11180,28 +11180,32 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5910.05</v>
+        <v>2870.04</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4020-1267-CM25</t>
+          <t>4455-840-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11226,12 +11230,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11241,17 +11245,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11260,13 +11264,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2870.04</v>
+        <v>8381.879999999999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4455-840-CM25</t>
+          <t>2418-78-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11291,12 +11295,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11306,26 +11310,22 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8381.879999999999</v>
+        <v>6930.5</v>
       </c>
     </row>
     <row r="171">
@@ -11782,7 +11782,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2418-94-CM25</t>
+          <t>2409-1714-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11802,17 +11802,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11841,13 +11841,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>12730.62</v>
+        <v>19307.75</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2759-1086-CM25</t>
+          <t>2418-94-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11867,17 +11867,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -11906,13 +11906,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>25320.82</v>
+        <v>12730.62</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2409-1714-CM25</t>
+          <t>2759-1086-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11952,17 +11952,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>19307.75</v>
+        <v>25320.82</v>
       </c>
     </row>
     <row r="181">
@@ -13891,7 +13891,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4494-34-CM26</t>
+          <t>3892-46-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -13950,13 +13950,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1039.05</v>
+        <v>3048.88</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3892-46-CM26</t>
+          <t>4494-34-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13996,12 +13996,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14015,13 +14015,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3048.88</v>
+        <v>1039.05</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2410-40-CM26</t>
+          <t>2410-43-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>11734.66</v>
+        <v>8032.5</v>
       </c>
     </row>
     <row r="214">
@@ -14151,7 +14151,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2410-43-CM26</t>
+          <t>2410-40-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14191,12 +14191,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14210,13 +14210,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>8032.5</v>
+        <v>11734.66</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2408-82-CM26</t>
+          <t>2408-81-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14275,13 +14275,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>35196.06</v>
+        <v>1872.11</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2408-81-CM26</t>
+          <t>2408-78-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14340,13 +14340,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1872.11</v>
+        <v>25160.98</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2408-78-CM26</t>
+          <t>2408-82-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -14405,7 +14405,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>25160.98</v>
+        <v>35196.06</v>
       </c>
     </row>
     <row r="219">
@@ -15435,7 +15435,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4377-84-CM26</t>
+          <t>4377-85-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15500,7 +15500,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4377-85-CM26</t>
+          <t>4377-84-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15565,7 +15565,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2418-8-CM26</t>
+          <t>4856-67-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15605,12 +15605,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>8741.5</v>
+        <v>957.36</v>
       </c>
     </row>
     <row r="238">
@@ -15691,7 +15691,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4856-67-CM26</t>
+          <t>2418-8-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15716,12 +15716,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15731,12 +15731,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -15750,7 +15750,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>957.36</v>
+        <v>8741.5</v>
       </c>
     </row>
     <row r="240">
@@ -16191,7 +16191,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4494-178-CM26</t>
+          <t>2785-223-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>7350.63</v>
+        <v>2094.4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2785-223-CM26</t>
+          <t>4494-178-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16281,12 +16281,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16296,12 +16296,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2094.4</v>
+        <v>7350.63</v>
       </c>
     </row>
     <row r="249">
@@ -16443,7 +16443,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3567-188-CM26</t>
+          <t>3567-189-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16483,28 +16483,32 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>11431.85</v>
+        <v>3192.01</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3567-189-CM26</t>
+          <t>3567-188-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16544,26 +16548,22 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3192.01</v>
+        <v>11431.85</v>
       </c>
     </row>
     <row r="253">
@@ -16764,7 +16764,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2410-191-CM26</t>
+          <t>4560-218-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.160.401-2</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16804,28 +16804,32 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>8158.76</v>
+        <v>12436.45</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4560-218-CM26</t>
+          <t>2410-191-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16850,12 +16854,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.160.401-2</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16865,26 +16869,22 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>12436.45</v>
+        <v>8158.76</v>
       </c>
     </row>
     <row r="258">
@@ -17719,7 +17719,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4189-246-CM26</t>
+          <t>4493-274-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17739,17 +17739,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17759,22 +17759,26 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>13280.19</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="272">
@@ -17845,7 +17849,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>4493-274-CM26</t>
+          <t>4189-246-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17865,17 +17869,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.150.502-2</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17885,32 +17889,28 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>755.64</v>
+        <v>13280.19</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4081-180-CM26</t>
+          <t>4081-181-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17969,13 +17969,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1530.08</v>
+        <v>2295.12</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4081-181-CM26</t>
+          <t>4081-180-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18034,13 +18034,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2295.12</v>
+        <v>1530.08</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4081-191-CM26</t>
+          <t>4081-190-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18080,32 +18080,28 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>674.73</v>
+        <v>2024.19</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4081-190-CM26</t>
+          <t>4081-191-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18145,22 +18141,26 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2024.19</v>
+        <v>674.73</v>
       </c>
     </row>
     <row r="278">
@@ -18686,7 +18686,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3945-373-CM26</t>
+          <t>3085-366-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18741,13 +18741,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>41919.88</v>
+        <v>23944.42</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3085-366-CM26</t>
+          <t>3945-373-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18772,12 +18772,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18802,7 +18802,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>23944.42</v>
+        <v>41919.88</v>
       </c>
     </row>
     <row r="288">
@@ -19060,7 +19060,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1456839-44-CM26</t>
+          <t>1456839-47-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19100,12 +19100,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -19119,7 +19119,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1646.72</v>
+        <v>1412.22</v>
       </c>
     </row>
     <row r="293">
@@ -19190,7 +19190,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1456839-47-CM26</t>
+          <t>1456839-44-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19230,12 +19230,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -19249,7 +19249,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1412.22</v>
+        <v>1646.72</v>
       </c>
     </row>
     <row r="295">
@@ -19320,7 +19320,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2421-756-CM26</t>
+          <t>4020-548-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19360,28 +19360,32 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>11012.63</v>
+        <v>1009.42</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4020-548-CM26</t>
+          <t>2421-756-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19406,12 +19410,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19421,26 +19425,22 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1009.42</v>
+        <v>11012.63</v>
       </c>
     </row>
     <row r="298">
@@ -19511,7 +19511,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>4081-230-CM26</t>
+          <t>4081-232-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19570,13 +19570,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1250.19</v>
+        <v>534.3099999999999</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4081-232-CM26</t>
+          <t>4081-230-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>534.3099999999999</v>
+        <v>1250.19</v>
       </c>
     </row>
     <row r="301">
@@ -19828,7 +19828,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2408-667-CM26</t>
+          <t>1467968-21-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19853,12 +19853,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>65.633.180-1</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>CORPORACION CULTURAL DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19868,12 +19868,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -19887,13 +19887,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>3875.08</v>
+        <v>2130.08</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1467968-21-CM26</t>
+          <t>2408-667-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19918,12 +19918,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>65.633.180-1</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19933,12 +19933,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -19952,7 +19952,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2130.08</v>
+        <v>3875.08</v>
       </c>
     </row>
     <row r="306">
@@ -20344,7 +20344,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4358-140-CM26</t>
+          <t>2418-50-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20364,17 +20364,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20384,17 +20384,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20403,13 +20403,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>18368.08</v>
+        <v>9612.82</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2418-50-CM26</t>
+          <t>4358-140-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20429,17 +20429,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20449,17 +20449,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -20468,7 +20468,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>9612.82</v>
+        <v>18368.08</v>
       </c>
     </row>
     <row r="314">
@@ -20799,7 +20799,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2665-384-CM26</t>
+          <t>2665-381-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20839,12 +20839,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -20858,13 +20858,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>17835.86</v>
+        <v>5940.54</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2665-380-CM26</t>
+          <t>2665-384-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20904,12 +20904,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>33945.94</v>
+        <v>17835.86</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2665-381-CM26</t>
+          <t>1375757-431-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20949,17 +20949,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20969,12 +20969,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -20988,13 +20988,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>5940.54</v>
+        <v>7006.95</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2665-383-CM26</t>
+          <t>2665-380-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21034,12 +21034,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -21053,13 +21053,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>26753.79</v>
+        <v>33945.94</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1375757-431-CM26</t>
+          <t>2665-383-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21079,17 +21079,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21118,7 +21118,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>7006.95</v>
+        <v>26753.79</v>
       </c>
     </row>
     <row r="324">
@@ -21770,7 +21770,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4858-802-CM26</t>
+          <t>4858-803-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21810,32 +21810,28 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>567</v>
+        <v>1803.78</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4858-803-CM26</t>
+          <t>4858-802-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21875,22 +21871,26 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1803.78</v>
+        <v>567</v>
       </c>
     </row>
     <row r="336">
@@ -21981,7 +21981,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -22026,7 +22026,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1143-176-CM26</t>
+          <t>1629-104-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22051,12 +22051,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>60.511.080-0</t>
+          <t>60.511.083-5</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL BIOBÍO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ARAUCO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1629-104-CM26</t>
+          <t>2785-663-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22181,12 +22181,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>60.511.083-5</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22196,12 +22196,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -22215,13 +22215,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3152.31</v>
+        <v>736.37</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2785-663-CM26</t>
+          <t>1143-176-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22246,12 +22246,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>60.511.080-0</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22261,12 +22261,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -22280,7 +22280,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>736.37</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="342">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -22412,7 +22412,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>732434-267-CM26</t>
+          <t>2421-1140-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22432,17 +22432,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>65.913.720-8</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22452,32 +22452,28 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>37571.89</v>
+        <v>2705.67</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2421-1140-CM26</t>
+          <t>732434-267-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22497,17 +22493,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>65.913.720-8</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22517,22 +22513,26 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2705.67</v>
+        <v>37571.89</v>
       </c>
     </row>
     <row r="346">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -22598,6 +22598,575 @@
       </c>
       <c r="M346" s="2" t="n">
         <v>736.37</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>4236-707-CM26</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>69.160.200-1</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>29170.05</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1208910-262-CM26</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>65.201.852-1</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="n">
+        <v>37485</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1208910-263-CM26</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>65.201.852-1</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>1259.88</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>3945-730-CM26</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>69.160.400-4</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="n">
+        <v>2948.11</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2771-637-CM26</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>69.264.700-9</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="n">
+        <v>672.35</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>952751-351-CM26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>74.269.600-6</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="n">
+        <v>16200.18</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>952751-356-CM26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>74.269.600-6</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="n">
+        <v>834.1900000000001</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1036-281-CM26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="n">
+        <v>804.39</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1305504-211-CM26</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>61.981.100-3</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="n">
+        <v>3619.77</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/biobio.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/biobio.xlsx
@@ -20624,7 +20624,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
